--- a/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-score-modifizierte-rankin-skala.xlsx
+++ b/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-score-modifizierte-rankin-skala.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:44:58+00:00</t>
+    <t>2026-09-01T20:00:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-score-modifizierte-rankin-skala.xlsx
+++ b/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-score-modifizierte-rankin-skala.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T20:00:38+00:00</t>
+    <t>2026-09-03T15:07:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-score-modifizierte-rankin-skala.xlsx
+++ b/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-score-modifizierte-rankin-skala.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T15:07:11+00:00</t>
+    <t>2026-09-04T19:01:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
